--- a/evalute_grading_results_metrics.xlsx
+++ b/evalute_grading_results_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UEH\Downloads\17. Đề án tốt nghiệp\rag\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BEFDD5-891F-4E4A-B11D-E265C5F70626}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CA73B2-DFA0-41B1-A36D-4C151216C112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>Chiến lược kinh doanh thương mại điện tử</t>
   </si>
@@ -613,6 +613,49 @@
   </si>
   <si>
     <t>diem_mo_hinh_norag</t>
+  </si>
+  <si>
+    <t>nhom5.pdf</t>
+  </si>
+  <si>
+    <t>ĐẠI HỌC UEH
+TRƯỜNG CÔNG NGHỆ VÀ THIẾT KẾ
+KHOA CÔNG NGHỆ THÔNG TIN KINH DOANH
+ĐỒ ÁN: XÂY DỰNG CHIẾN LƯỢC MARKETING KỸ THUẬT SỐ CHO
+STRONGBOW SPARKLING CIDER
+BỘ MÔN MARKETING KỸ THUẬT SỐ
+GVHD: TS Nguyễn Thành Huy
+Thành viên nhóm E: Nguyễn Lê Trúc Anh
+Đỗ Thanh Hoa
+Nguyễn Huy Hoàng
+Nguyễn Bảo Cát Minh
+L...</t>
+  </si>
+  <si>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+MỤC LỤC
+MỤC LỤC ........................................................................................................................... 1
+DANH MỤC CÁC BẢNG ................................................................................................. 4
+DANH MỤC HÌNH ẢNH ........................</t>
+  </si>
+  <si>
+    <t>Chiến lược Digital Marketing cho sản
+phẩm
+TH true YOGURT TOP CUP
+Môn học: Digital Marketing
+Lớp: 24C1INF50903201
+Giảng viên hướng dẫn: TS. Nguyễn Thành Huy
+Nhóm sinh viên thực hiện: Nhóm H:
+Nguyễn Trần Thế Anh 31221026655
+Phạm Bằng 31221024364
+Nguyễn Huỳnh Hương Giao 31221021656
+Trương Phạm Bảo Khan...</t>
+  </si>
+  <si>
+    <t>9.3</t>
   </si>
 </sst>
 </file>
@@ -648,10 +691,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -955,11 +1001,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="51.5703125" customWidth="1"/>
     <col min="4" max="4" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -1268,122 +1314,113 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="1">
-        <v>7</v>
-      </c>
-      <c r="F16" s="1">
+        <v>87</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="F17" s="2">
         <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="1">
-        <v>7</v>
-      </c>
-      <c r="F17" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="1">
-        <v>7</v>
-      </c>
-      <c r="F18" s="1">
-        <v>8</v>
+        <v>90</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="2">
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E19" s="1">
         <v>7</v>
       </c>
       <c r="F19" s="1">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="1">
-        <v>9.35</v>
+        <v>38</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="E20" s="1">
         <v>7</v>
       </c>
       <c r="F20" s="1">
-        <v>8.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E21" s="1">
         <v>7</v>
       </c>
       <c r="F21" s="1">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1391,19 +1428,19 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E22" s="1">
         <v>7</v>
       </c>
       <c r="F22" s="1">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1411,19 +1448,19 @@
         <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D23" s="1">
-        <v>6.8</v>
+        <v>9.35</v>
       </c>
       <c r="E23" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="1">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1431,19 +1468,19 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E24" s="1">
         <v>7</v>
       </c>
       <c r="F24" s="1">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1451,19 +1488,19 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E25" s="1">
         <v>7</v>
       </c>
       <c r="F25" s="1">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1471,19 +1508,19 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="D26" s="1">
+        <v>6.8</v>
       </c>
       <c r="E26" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" s="1">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1491,19 +1528,19 @@
         <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E27" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F27" s="1">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1511,19 +1548,19 @@
         <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E28" s="1">
         <v>7</v>
       </c>
       <c r="F28" s="1">
-        <v>8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1531,19 +1568,19 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="E29" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" s="1">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1551,19 +1588,19 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="E30" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1571,19 +1608,19 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="E31" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1591,16 +1628,16 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" s="1">
-        <v>7.3</v>
+        <v>69</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" s="1">
         <v>7.5</v>
@@ -1611,10 +1648,10 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>3</v>
@@ -1631,10 +1668,10 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>3</v>
@@ -1643,6 +1680,66 @@
         <v>6</v>
       </c>
       <c r="F34" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>7</v>
+      </c>
+      <c r="F35" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>7</v>
+      </c>
+      <c r="F36" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>6</v>
+      </c>
+      <c r="F37" s="1">
         <v>7.5</v>
       </c>
     </row>
